--- a/output/pdf_financials_xlsx/ELO.xlsx
+++ b/output/pdf_financials_xlsx/ELO.xlsx
@@ -2697,37 +2697,37 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.233678</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.22759</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.254445</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.546921</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.042448</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.010339</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.255305</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.080743</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.026096</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.435379</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.031328</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.015421</v>
@@ -2829,37 +2829,37 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.021</v>
+        <v>0.254678</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.11275</v>
+        <v>1.34034</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.128125</v>
+        <v>1.38257</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.0655</v>
+        <v>0.612421</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.02425</v>
+        <v>0.06669799999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.07074999999999999</v>
+        <v>0.08108899999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.076034</v>
+        <v>0.331339</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.00769</v>
+        <v>0.088433</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.278292</v>
+        <v>0.304388</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.198055</v>
+        <v>0.6334340000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.1589</v>
+        <v>0.190228</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0.044671</v>
@@ -3621,37 +3621,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.312101</v>
+        <v>0.07842300000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.365797</v>
+        <v>0.138207</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.283682</v>
+        <v>0.029237</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.574156</v>
+        <v>0.027235</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.048698</v>
+        <v>0.00625</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.019973</v>
+        <v>0.009634</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.310312</v>
+        <v>0.055007</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.107044</v>
+        <v>0.026301</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.079457</v>
+        <v>0.053361</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.569258</v>
+        <v>0.133879</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.347321</v>
+        <v>0.315993</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.055263</v>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">

--- a/output/pdf_financials_xlsx/ELO.xlsx
+++ b/output/pdf_financials_xlsx/ELO.xlsx
@@ -1441,25 +1441,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2.933871</v>
+        <v>-2.933871</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.379</v>
+        <v>-0.379</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.634</v>
+        <v>-0.634</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.056133</v>
+        <v>-1.056133</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.831362</v>
+        <v>-0.831362</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.085894</v>
+        <v>0.085894</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1.026106</v>
+        <v>-1.026106</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.081</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -8191,13 +8191,13 @@
         <v>0</v>
       </c>
       <c r="R114" s="3" t="n">
-        <v>0</v>
+        <v>-0.901945</v>
       </c>
       <c r="S114" s="3" t="n">
-        <v>0</v>
+        <v>-0.027358</v>
       </c>
       <c r="T114" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="115">
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.066265</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.008524</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -8231,7 +8231,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.07446</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -8240,13 +8240,13 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.097773</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.052995</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.007805</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
@@ -8255,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.106881</v>
       </c>
       <c r="S115" s="3" t="n">
         <v>0</v>
@@ -21241,7 +21241,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="n">
         <v>-0.081</v>
       </c>
@@ -23660,7 +23664,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="n">
         <v>0.066265</v>
       </c>
@@ -29421,7 +29429,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -29976,7 +29988,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -30737,7 +30753,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -32049,7 +32069,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -34033,7 +34057,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E230" s="5" t="n">
         <v>-2.933871</v>
       </c>
@@ -44955,7 +44983,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -45617,7 +45649,11 @@
           <t>Deferred income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -45837,7 +45873,11 @@
           <t>Deferred income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -45946,7 +45986,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -48223,7 +48267,11 @@
           <t>Future income tax recovery (note 9)</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E362" s="5" t="n">
         <v>2.933871</v>
       </c>
@@ -49083,7 +49131,11 @@
           <t>Future income tax recovery (note 8)</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E370" s="5" t="n">
         <v>1.840488</v>
       </c>
